--- a/data/trans_camb/P57_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Habitat-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 1,22</t>
+          <t>-6,76; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -0,81</t>
+          <t>-9,12; -0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -0,85</t>
+          <t>-6,63; -0,76</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 7,15</t>
+          <t>-32,02; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,91; -3,7</t>
+          <t>-33,9; -3,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,04; -4,45</t>
+          <t>-28,27; -3,7</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -6,55</t>
+          <t>-16,05; -6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,21</t>
+          <t>-9,77; -3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -6,24</t>
+          <t>-13,19; -6,3</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,42; -35,55</t>
+          <t>-75,8; -34,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,49; -14,94</t>
+          <t>-37,69; -13,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -30,18</t>
+          <t>-61,66; -30,24</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -5,02</t>
+          <t>-11,81; -4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,47; -8,4</t>
+          <t>-17,31; -8,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -7,56</t>
+          <t>-13,68; -7,66</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,51; -31,35</t>
+          <t>-62,04; -30,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,91; -46,05</t>
+          <t>-81,13; -47,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -43,17</t>
+          <t>-71,25; -44,93</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,12</t>
+          <t>-4,68; 2,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -2,79</t>
+          <t>-10,88; -2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -1,27</t>
+          <t>-6,6; -1,39</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 13,32</t>
+          <t>-24,55; 14,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -11,52</t>
+          <t>-40,58; -11,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,9; -6,09</t>
+          <t>-28,78; -6,97</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,84</t>
+          <t>-9,03; -4,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -5,58</t>
+          <t>-10,83; -5,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -5,31</t>
+          <t>-9,06; -5,46</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,62; -22,16</t>
+          <t>-47,72; -22,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -25,08</t>
+          <t>-45,26; -24,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -26,16</t>
+          <t>-41,21; -26,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,79</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,65</t>
+          <t>-3,85</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,43</t>
+          <t>-7,16; 1,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,68</t>
+          <t>-9,43; -0,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,76</t>
+          <t>-6,86; -0,91</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-13,77%</t>
+          <t>-16,18%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-19,89%</t>
+          <t>-19,74%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,96%</t>
+          <t>-17,91%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 9,13</t>
+          <t>-33,75; 6,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,9; -3,2</t>
+          <t>-34,28; -3,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,27; -3,7</t>
+          <t>-29,26; -4,75</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-10,46</t>
+          <t>-8,02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,01</t>
+          <t>-7,23</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -6,47</t>
+          <t>-11,49; -4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -3,03</t>
+          <t>-9,85; -2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -6,3</t>
+          <t>-9,48; -4,86</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-52,03%</t>
+          <t>-39,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-28,09%</t>
+          <t>-27,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-41,02%</t>
+          <t>-32,91%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,8; -34,24</t>
+          <t>-52,03; -26,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; -13,91</t>
+          <t>-37,78; -12,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,66; -30,24</t>
+          <t>-40,79; -23,82</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-8,42</t>
+          <t>-8,29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-12,08</t>
+          <t>-9,29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-10,37</t>
+          <t>-8,81</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -4,63</t>
+          <t>-11,79; -4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -8,52</t>
+          <t>-13,08; -5,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -7,66</t>
+          <t>-11,24; -6,3</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-48,62%</t>
+          <t>-47,88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-61,9%</t>
+          <t>-47,6%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-56,24%</t>
+          <t>-47,77%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,04; -30,57</t>
+          <t>-60,11; -31,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,13; -47,15</t>
+          <t>-59,45; -33,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,25; -44,93</t>
+          <t>-56,49; -36,54</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-6,19</t>
+          <t>-4,68</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-2,85</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,31</t>
+          <t>-4,54; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -2,34</t>
+          <t>-8,49; -0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -1,39</t>
+          <t>-5,45; -0,29</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-7,35%</t>
+          <t>-4,8%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-24,06%</t>
+          <t>-18,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-17,51%</t>
+          <t>-13,05%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 14,17</t>
+          <t>-22,65; 16,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,58; -11,11</t>
+          <t>-29,82; -3,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,78; -6,97</t>
+          <t>-23,56; -1,33</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-6,06</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -4,03</t>
+          <t>-7,0; -3,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -5,58</t>
+          <t>-8,11; -4,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -5,46</t>
+          <t>-6,9; -4,46</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-32,71%</t>
+          <t>-27,66%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-32,82%</t>
+          <t>-26,32%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-26,85%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -22,9</t>
+          <t>-35,2; -18,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,26; -24,65</t>
+          <t>-33,17; -19,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -26,63</t>
+          <t>-32,08; -21,9</t>
         </is>
       </c>
     </row>
